--- a/ExperimentLogs.xlsx
+++ b/ExperimentLogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliverstaub/gitroot/BachelorThesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831589B3-9D91-AA4C-A973-810E331C52DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF90E13-05B6-0145-A9F6-5E1DE5D19FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15120" yWindow="680" windowWidth="15120" windowHeight="17960" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="10080" windowHeight="17940" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Experiments" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="112">
   <si>
     <t>Website-Fingerprinting Experiment Tracker  —  Tor Circuit Padding Study</t>
   </si>
@@ -765,7 +765,10 @@
     <t>If accuracy holds across these splits, the classifier is learning page features rather than network artefacts.</t>
   </si>
   <si>
-    <t>python3 shadowctl.py run exp-baseline --pages 20 --visits 100 --padding off</t>
+    <t>OFF</t>
+  </si>
+  <si>
+    <t>exp-baseline-20</t>
   </si>
 </sst>
 </file>
@@ -777,7 +780,7 @@
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\-0.0%;\-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -826,6 +829,25 @@
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -928,22 +950,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -987,8 +995,25 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="21" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1253,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF23"/>
+  <dimension ref="A1:AF22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -1281,1006 +1306,1091 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="6"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="6"/>
-      <c r="AF1" s="6"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="16"/>
+      <c r="AF1" s="16"/>
     </row>
     <row r="2" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="4" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="3" t="s">
+      <c r="Q2" s="18"/>
+      <c r="R2" s="18"/>
+      <c r="S2" s="18"/>
+      <c r="T2" s="18"/>
+      <c r="U2" s="18"/>
+      <c r="V2" s="18"/>
+      <c r="W2" s="18"/>
+      <c r="X2" s="18"/>
+      <c r="Y2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
-      <c r="AF2" s="3"/>
+      <c r="Z2" s="19"/>
+      <c r="AA2" s="19"/>
+      <c r="AB2" s="19"/>
+      <c r="AC2" s="19"/>
+      <c r="AD2" s="19"/>
+      <c r="AE2" s="19"/>
+      <c r="AF2" s="19"/>
     </row>
     <row r="3" spans="1:32" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="P3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="R3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="S3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="T3" s="8" t="s">
+      <c r="T3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="U3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="V3" s="8" t="s">
+      <c r="V3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W3" s="8" t="s">
+      <c r="W3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="X3" s="8" t="s">
+      <c r="X3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Y3" s="9" t="s">
+      <c r="Y3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="Z3" s="9" t="s">
+      <c r="Z3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AA3" s="9" t="s">
+      <c r="AA3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AB3" s="9" t="s">
+      <c r="AB3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AC3" s="9" t="s">
+      <c r="AC3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AD3" s="9" t="s">
+      <c r="AD3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AE3" s="9" t="s">
+      <c r="AE3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AF3" s="9" t="s">
+      <c r="AF3" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="5">
         <v>0.01</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="6">
         <v>79</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="6">
         <v>3</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="6">
         <v>82</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="6">
         <v>5</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="6">
         <v>5</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="6">
         <v>50</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="6">
         <v>30</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="10"/>
-      <c r="L4" s="12">
+      <c r="K4" s="4"/>
+      <c r="L4" s="6">
         <v>1</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="N4" s="12">
+      <c r="N4" s="6">
         <v>3600</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P4" s="12">
+      <c r="P4" s="6">
         <v>250</v>
       </c>
-      <c r="Q4" s="12">
+      <c r="Q4" s="6">
         <v>50</v>
       </c>
-      <c r="R4" s="12">
+      <c r="R4" s="6">
         <v>9</v>
       </c>
-      <c r="S4" s="14">
-        <f t="shared" ref="S4:S23" si="0">IFERROR(R4/P4,"")</f>
+      <c r="S4" s="8">
+        <f t="shared" ref="S4:S22" si="0">IFERROR(R4/P4,"")</f>
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="T4" s="12">
+      <c r="T4" s="6">
         <v>0</v>
       </c>
-      <c r="U4" s="12">
+      <c r="U4" s="6">
         <v>804</v>
       </c>
-      <c r="V4" s="12">
+      <c r="V4" s="6">
         <v>202</v>
       </c>
-      <c r="W4" s="12">
+      <c r="W4" s="6">
         <v>23</v>
       </c>
-      <c r="X4" s="12">
+      <c r="X4" s="6">
         <v>25</v>
       </c>
-      <c r="Y4" s="14">
+      <c r="Y4" s="8">
         <v>0.32</v>
       </c>
-      <c r="Z4" s="14">
+      <c r="Z4" s="8">
         <v>0.45600000000000002</v>
       </c>
-      <c r="AA4" s="14">
+      <c r="AA4" s="8">
         <v>0.32</v>
       </c>
-      <c r="AB4" s="14">
+      <c r="AB4" s="8">
         <v>0.26800000000000002</v>
       </c>
-      <c r="AC4" s="12">
+      <c r="AC4" s="6">
         <v>30</v>
       </c>
-      <c r="AD4" s="12">
+      <c r="AD4" s="6">
         <v>29</v>
       </c>
-      <c r="AE4" s="14">
-        <f t="shared" ref="AE4:AE23" si="1">IFERROR(1/G4,"")</f>
+      <c r="AE4" s="8">
+        <f t="shared" ref="AE4:AE22" si="1">IFERROR(1/G4,"")</f>
         <v>0.2</v>
       </c>
-      <c r="AF4" s="15" t="s">
+      <c r="AF4" s="9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="14" t="str">
+    <row r="5" spans="1:32" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="23">
+        <v>0.01</v>
+      </c>
+      <c r="C5" s="23">
+        <v>79</v>
+      </c>
+      <c r="D5" s="23">
+        <v>3</v>
+      </c>
+      <c r="E5" s="23">
+        <v>298</v>
+      </c>
+      <c r="F5" s="23">
+        <v>5</v>
+      </c>
+      <c r="G5" s="23">
+        <v>5</v>
+      </c>
+      <c r="H5" s="23">
+        <v>100</v>
+      </c>
+      <c r="I5" s="23">
+        <v>30</v>
+      </c>
+      <c r="J5" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="K5" s="24"/>
+      <c r="L5" s="23">
+        <v>1</v>
+      </c>
+      <c r="M5" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="N5" s="24"/>
+      <c r="O5" s="25">
+        <v>0.13750000000000001</v>
+      </c>
+      <c r="P5" s="23">
+        <v>500</v>
+      </c>
+      <c r="Q5" s="23">
+        <v>100</v>
+      </c>
+      <c r="R5" s="23">
+        <v>22</v>
+      </c>
+      <c r="S5" s="26">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="T5" s="24"/>
+      <c r="U5" s="23">
+        <v>787</v>
+      </c>
+      <c r="V5" s="23">
+        <v>405</v>
+      </c>
+      <c r="W5" s="23">
+        <v>45</v>
+      </c>
+      <c r="X5" s="23">
+        <v>50</v>
+      </c>
+      <c r="Y5" s="26">
+        <v>0.92</v>
+      </c>
+      <c r="Z5" s="26">
+        <v>0.93600000000000005</v>
+      </c>
+      <c r="AA5" s="26">
+        <v>0.92</v>
+      </c>
+      <c r="AB5" s="26">
+        <v>0.92100000000000004</v>
+      </c>
+      <c r="AC5" s="23">
+        <v>30</v>
+      </c>
+      <c r="AD5" s="24"/>
+      <c r="AE5" s="26">
+        <v>0.2</v>
+      </c>
+      <c r="AF5" s="24"/>
+    </row>
+    <row r="6" spans="1:32" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="23">
+        <v>0.01</v>
+      </c>
+      <c r="C6" s="23">
+        <v>79</v>
+      </c>
+      <c r="D6" s="23">
+        <v>3</v>
+      </c>
+      <c r="E6" s="23">
+        <v>303</v>
+      </c>
+      <c r="F6" s="23">
+        <v>10</v>
+      </c>
+      <c r="G6" s="23">
+        <v>20</v>
+      </c>
+      <c r="H6" s="23">
+        <v>150</v>
+      </c>
+      <c r="I6" s="23">
+        <v>30</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="K6" s="24"/>
+      <c r="L6" s="23">
+        <v>1</v>
+      </c>
+      <c r="M6" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="N6" s="24"/>
+      <c r="O6" s="25">
+        <v>0.33124999999999999</v>
+      </c>
+      <c r="P6" s="23">
+        <v>3000</v>
+      </c>
+      <c r="Q6" s="23">
+        <v>150</v>
+      </c>
+      <c r="R6" s="23">
+        <v>51</v>
+      </c>
+      <c r="S6" s="26">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="T6" s="24"/>
+      <c r="U6" s="23">
+        <v>635</v>
+      </c>
+      <c r="V6" s="23">
+        <v>2430</v>
+      </c>
+      <c r="W6" s="23">
+        <v>270</v>
+      </c>
+      <c r="X6" s="23">
+        <v>300</v>
+      </c>
+      <c r="Y6" s="26">
+        <v>0.92700000000000005</v>
+      </c>
+      <c r="Z6" s="26">
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="AA6" s="26">
+        <v>0.92700000000000005</v>
+      </c>
+      <c r="AB6" s="26">
+        <v>0.92700000000000005</v>
+      </c>
+      <c r="AC6" s="23">
+        <v>30</v>
+      </c>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="26">
+        <v>0.05</v>
+      </c>
+      <c r="AF6" s="24"/>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="14"/>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="14"/>
-      <c r="AB5" s="14"/>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="12"/>
-      <c r="AE5" s="14" t="str">
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8"/>
+      <c r="AA7" s="8"/>
+      <c r="AB7" s="8"/>
+      <c r="AC7" s="6"/>
+      <c r="AD7" s="6"/>
+      <c r="AE7" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AF5" s="15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="14" t="str">
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="14"/>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="14"/>
-      <c r="AB6" s="14"/>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="12"/>
-      <c r="AE6" s="14" t="str">
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8"/>
+      <c r="AA8" s="8"/>
+      <c r="AB8" s="8"/>
+      <c r="AC8" s="6"/>
+      <c r="AD8" s="6"/>
+      <c r="AE8" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AF6" s="15"/>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="N7" s="22"/>
-      <c r="S7" s="23"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="23"/>
-      <c r="AA7" s="23"/>
-      <c r="AB7" s="23"/>
-      <c r="AE7" s="23"/>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="14" t="str">
+      <c r="AF8" s="9"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="14"/>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14"/>
-      <c r="AB8" s="14"/>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="12"/>
-      <c r="AE8" s="14" t="str">
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8"/>
+      <c r="AA9" s="8"/>
+      <c r="AB9" s="8"/>
+      <c r="AC9" s="6"/>
+      <c r="AD9" s="6"/>
+      <c r="AE9" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A9" s="10"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="14" t="str">
+      <c r="AF9" s="9"/>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="12"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="12"/>
-      <c r="Y9" s="14"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
-      <c r="AB9" s="14"/>
-      <c r="AC9" s="12"/>
-      <c r="AD9" s="12"/>
-      <c r="AE9" s="14" t="str">
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+      <c r="AA10" s="8"/>
+      <c r="AB10" s="8"/>
+      <c r="AC10" s="6"/>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AF9" s="15"/>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="14" t="str">
+      <c r="AF10" s="9"/>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="12"/>
-      <c r="Y10" s="14"/>
-      <c r="Z10" s="14"/>
-      <c r="AA10" s="14"/>
-      <c r="AB10" s="14"/>
-      <c r="AC10" s="12"/>
-      <c r="AD10" s="12"/>
-      <c r="AE10" s="14" t="str">
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="8"/>
+      <c r="AA11" s="8"/>
+      <c r="AB11" s="8"/>
+      <c r="AC11" s="6"/>
+      <c r="AD11" s="6"/>
+      <c r="AE11" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AF10" s="15"/>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="14" t="str">
+      <c r="AF11" s="9"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
-      <c r="X11" s="12"/>
-      <c r="Y11" s="14"/>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="14"/>
-      <c r="AB11" s="14"/>
-      <c r="AC11" s="12"/>
-      <c r="AD11" s="12"/>
-      <c r="AE11" s="14" t="str">
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8"/>
+      <c r="AA12" s="8"/>
+      <c r="AB12" s="8"/>
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6"/>
+      <c r="AE12" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AF11" s="15"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="14" t="str">
+      <c r="AF12" s="9"/>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="12"/>
-      <c r="Y12" s="14"/>
-      <c r="Z12" s="14"/>
-      <c r="AA12" s="14"/>
-      <c r="AB12" s="14"/>
-      <c r="AC12" s="12"/>
-      <c r="AD12" s="12"/>
-      <c r="AE12" s="14" t="str">
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="8"/>
+      <c r="AA13" s="8"/>
+      <c r="AB13" s="8"/>
+      <c r="AC13" s="6"/>
+      <c r="AD13" s="6"/>
+      <c r="AE13" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AF12" s="15"/>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="14" t="str">
+      <c r="AF13" s="9"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="12"/>
-      <c r="W13" s="12"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="14"/>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="14"/>
-      <c r="AB13" s="14"/>
-      <c r="AC13" s="12"/>
-      <c r="AD13" s="12"/>
-      <c r="AE13" s="14" t="str">
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="8"/>
+      <c r="AA14" s="8"/>
+      <c r="AB14" s="8"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AF13" s="15"/>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="14" t="str">
+      <c r="AF14" s="9"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="14"/>
-      <c r="Z14" s="14"/>
-      <c r="AA14" s="14"/>
-      <c r="AB14" s="14"/>
-      <c r="AC14" s="12"/>
-      <c r="AD14" s="12"/>
-      <c r="AE14" s="14" t="str">
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="8"/>
+      <c r="AA15" s="8"/>
+      <c r="AB15" s="8"/>
+      <c r="AC15" s="6"/>
+      <c r="AD15" s="6"/>
+      <c r="AE15" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AF14" s="15"/>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="14" t="str">
+      <c r="AF15" s="9"/>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T15" s="12"/>
-      <c r="U15" s="12"/>
-      <c r="V15" s="12"/>
-      <c r="W15" s="12"/>
-      <c r="X15" s="12"/>
-      <c r="Y15" s="14"/>
-      <c r="Z15" s="14"/>
-      <c r="AA15" s="14"/>
-      <c r="AB15" s="14"/>
-      <c r="AC15" s="12"/>
-      <c r="AD15" s="12"/>
-      <c r="AE15" s="14" t="str">
+      <c r="T16" s="6"/>
+      <c r="U16" s="6"/>
+      <c r="V16" s="6"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="8"/>
+      <c r="AA16" s="8"/>
+      <c r="AB16" s="8"/>
+      <c r="AC16" s="6"/>
+      <c r="AD16" s="6"/>
+      <c r="AE16" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AF15" s="15"/>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="14" t="str">
+      <c r="AF16" s="9"/>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T16" s="12"/>
-      <c r="U16" s="12"/>
-      <c r="V16" s="12"/>
-      <c r="W16" s="12"/>
-      <c r="X16" s="12"/>
-      <c r="Y16" s="14"/>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="14"/>
-      <c r="AB16" s="14"/>
-      <c r="AC16" s="12"/>
-      <c r="AD16" s="12"/>
-      <c r="AE16" s="14" t="str">
+      <c r="T17" s="6"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="8"/>
+      <c r="AA17" s="8"/>
+      <c r="AB17" s="8"/>
+      <c r="AC17" s="6"/>
+      <c r="AD17" s="6"/>
+      <c r="AE17" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AF16" s="15"/>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="14" t="str">
+      <c r="AF17" s="9"/>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T17" s="12"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="12"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12"/>
-      <c r="Y17" s="14"/>
-      <c r="Z17" s="14"/>
-      <c r="AA17" s="14"/>
-      <c r="AB17" s="14"/>
-      <c r="AC17" s="12"/>
-      <c r="AD17" s="12"/>
-      <c r="AE17" s="14" t="str">
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="6"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="8"/>
+      <c r="Z18" s="8"/>
+      <c r="AA18" s="8"/>
+      <c r="AB18" s="8"/>
+      <c r="AC18" s="6"/>
+      <c r="AD18" s="6"/>
+      <c r="AE18" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AF17" s="15"/>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="14" t="str">
+      <c r="AF18" s="9"/>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T18" s="12"/>
-      <c r="U18" s="12"/>
-      <c r="V18" s="12"/>
-      <c r="W18" s="12"/>
-      <c r="X18" s="12"/>
-      <c r="Y18" s="14"/>
-      <c r="Z18" s="14"/>
-      <c r="AA18" s="14"/>
-      <c r="AB18" s="14"/>
-      <c r="AC18" s="12"/>
-      <c r="AD18" s="12"/>
-      <c r="AE18" s="14" t="str">
+      <c r="T19" s="6"/>
+      <c r="U19" s="6"/>
+      <c r="V19" s="6"/>
+      <c r="W19" s="6"/>
+      <c r="X19" s="6"/>
+      <c r="Y19" s="8"/>
+      <c r="Z19" s="8"/>
+      <c r="AA19" s="8"/>
+      <c r="AB19" s="8"/>
+      <c r="AC19" s="6"/>
+      <c r="AD19" s="6"/>
+      <c r="AE19" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AF18" s="15"/>
-    </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="14" t="str">
+      <c r="AF19" s="9"/>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T19" s="12"/>
-      <c r="U19" s="12"/>
-      <c r="V19" s="12"/>
-      <c r="W19" s="12"/>
-      <c r="X19" s="12"/>
-      <c r="Y19" s="14"/>
-      <c r="Z19" s="14"/>
-      <c r="AA19" s="14"/>
-      <c r="AB19" s="14"/>
-      <c r="AC19" s="12"/>
-      <c r="AD19" s="12"/>
-      <c r="AE19" s="14" t="str">
+      <c r="T20" s="6"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="6"/>
+      <c r="W20" s="6"/>
+      <c r="X20" s="6"/>
+      <c r="Y20" s="8"/>
+      <c r="Z20" s="8"/>
+      <c r="AA20" s="8"/>
+      <c r="AB20" s="8"/>
+      <c r="AC20" s="6"/>
+      <c r="AD20" s="6"/>
+      <c r="AE20" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AF19" s="15"/>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="12"/>
-      <c r="Q20" s="12"/>
-      <c r="R20" s="12"/>
-      <c r="S20" s="14" t="str">
+      <c r="AF20" s="9"/>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T20" s="12"/>
-      <c r="U20" s="12"/>
-      <c r="V20" s="12"/>
-      <c r="W20" s="12"/>
-      <c r="X20" s="12"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
-      <c r="AB20" s="14"/>
-      <c r="AC20" s="12"/>
-      <c r="AD20" s="12"/>
-      <c r="AE20" s="14" t="str">
+      <c r="T21" s="6"/>
+      <c r="U21" s="6"/>
+      <c r="V21" s="6"/>
+      <c r="W21" s="6"/>
+      <c r="X21" s="6"/>
+      <c r="Y21" s="8"/>
+      <c r="Z21" s="8"/>
+      <c r="AA21" s="8"/>
+      <c r="AB21" s="8"/>
+      <c r="AC21" s="6"/>
+      <c r="AD21" s="6"/>
+      <c r="AE21" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AF20" s="15"/>
-    </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A21" s="10"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="12"/>
-      <c r="R21" s="12"/>
-      <c r="S21" s="14" t="str">
+      <c r="AF21" s="9"/>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T21" s="12"/>
-      <c r="U21" s="12"/>
-      <c r="V21" s="12"/>
-      <c r="W21" s="12"/>
-      <c r="X21" s="12"/>
-      <c r="Y21" s="14"/>
-      <c r="Z21" s="14"/>
-      <c r="AA21" s="14"/>
-      <c r="AB21" s="14"/>
-      <c r="AC21" s="12"/>
-      <c r="AD21" s="12"/>
-      <c r="AE21" s="14" t="str">
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="6"/>
+      <c r="Y22" s="8"/>
+      <c r="Z22" s="8"/>
+      <c r="AA22" s="8"/>
+      <c r="AB22" s="8"/>
+      <c r="AC22" s="6"/>
+      <c r="AD22" s="6"/>
+      <c r="AE22" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AF21" s="15"/>
-    </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
-      <c r="S22" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="T22" s="12"/>
-      <c r="U22" s="12"/>
-      <c r="V22" s="12"/>
-      <c r="W22" s="12"/>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14"/>
-      <c r="AB22" s="14"/>
-      <c r="AC22" s="12"/>
-      <c r="AD22" s="12"/>
-      <c r="AE22" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AF22" s="15"/>
-    </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A23" s="10"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
-      <c r="R23" s="12"/>
-      <c r="S23" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="T23" s="12"/>
-      <c r="U23" s="12"/>
-      <c r="V23" s="12"/>
-      <c r="W23" s="12"/>
-      <c r="X23" s="12"/>
-      <c r="Y23" s="14"/>
-      <c r="Z23" s="14"/>
-      <c r="AA23" s="14"/>
-      <c r="AB23" s="14"/>
-      <c r="AC23" s="12"/>
-      <c r="AD23" s="12"/>
-      <c r="AE23" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AF23" s="15"/>
+      <c r="AF22" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2290,7 +2400,7 @@
     <mergeCell ref="Y2:AF2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="J4:J23" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J4 J7:J22" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"OFF,ON,Reduced"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2314,195 +2424,195 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="12">
-        <f>IFERROR(INDEX(Experiments!$G$4:$G$23,MATCH($A4,Experiments!$A$4:$A$23,0)),"")</f>
+      <c r="B4" s="6">
+        <f>IFERROR(INDEX(Experiments!$G$4:$G$22,MATCH($A4,Experiments!$A$4:$A$22,0)),"")</f>
         <v>5</v>
       </c>
-      <c r="C4" s="12">
-        <f>IFERROR(INDEX(Experiments!$H$4:$H$23,MATCH($A4,Experiments!$A$4:$A$23,0)),"")</f>
+      <c r="C4" s="6">
+        <f>IFERROR(INDEX(Experiments!$H$4:$H$22,MATCH($A4,Experiments!$A$4:$A$22,0)),"")</f>
         <v>50</v>
       </c>
-      <c r="D4" s="10" t="str">
-        <f>IFERROR(INDEX(Experiments!$J$4:$J$23,MATCH($A4,Experiments!$A$4:$A$23,0)),"")</f>
+      <c r="D4" s="4" t="str">
+        <f>IFERROR(INDEX(Experiments!$J$4:$J$22,MATCH($A4,Experiments!$A$4:$A$22,0)),"")</f>
         <v>ON</v>
       </c>
-      <c r="E4" s="14">
-        <f>IFERROR(INDEX(Experiments!$Y$4:$Y$23,MATCH($A4,Experiments!$A$4:$A$23,0)),"")</f>
+      <c r="E4" s="8">
+        <f>IFERROR(INDEX(Experiments!$Y$4:$Y$22,MATCH($A4,Experiments!$A$4:$A$22,0)),"")</f>
         <v>0.32</v>
       </c>
-      <c r="F4" s="14">
-        <f>IFERROR(INDEX(Experiments!$AB$4:$AB$23,MATCH($A4,Experiments!$A$4:$A$23,0)),"")</f>
+      <c r="F4" s="8">
+        <f>IFERROR(INDEX(Experiments!$AB$4:$AB$22,MATCH($A4,Experiments!$A$4:$A$22,0)),"")</f>
         <v>0.26800000000000002</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="11" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="10" t="str">
-        <f>IFERROR(INDEX(Experiments!$G$4:$G$23,MATCH($A5,Experiments!$A$4:$A$23,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C5" s="10" t="str">
-        <f>IFERROR(INDEX(Experiments!$H$4:$H$23,MATCH($A5,Experiments!$A$4:$A$23,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D5" s="10" t="str">
-        <f>IFERROR(INDEX(Experiments!$J$4:$J$23,MATCH($A5,Experiments!$A$4:$A$23,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E5" s="14" t="str">
-        <f>IFERROR(INDEX(Experiments!$Y$4:$Y$23,MATCH($A5,Experiments!$A$4:$A$23,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F5" s="14" t="str">
-        <f>IFERROR(INDEX(Experiments!$AB$4:$AB$23,MATCH($A5,Experiments!$A$4:$A$23,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G5" s="17" t="s">
+      <c r="B5" s="4">
+        <f>IFERROR(INDEX(Experiments!$G$4:$G$22,MATCH($A5,Experiments!$A$4:$A$22,0)),"")</f>
+        <v>5</v>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(INDEX(Experiments!$H$4:$H$22,MATCH($A5,Experiments!$A$4:$A$22,0)),"")</f>
+        <v>100</v>
+      </c>
+      <c r="D5" s="4" t="str">
+        <f>IFERROR(INDEX(Experiments!$J$4:$J$22,MATCH($A5,Experiments!$A$4:$A$22,0)),"")</f>
+        <v>OFF</v>
+      </c>
+      <c r="E5" s="8">
+        <f>IFERROR(INDEX(Experiments!$Y$4:$Y$22,MATCH($A5,Experiments!$A$4:$A$22,0)),"")</f>
+        <v>0.92</v>
+      </c>
+      <c r="F5" s="8">
+        <f>IFERROR(INDEX(Experiments!$AB$4:$AB$22,MATCH($A5,Experiments!$A$4:$A$22,0)),"")</f>
+        <v>0.92100000000000004</v>
+      </c>
+      <c r="G5" s="11" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="10" t="str">
-        <f>IFERROR(INDEX(Experiments!$G$4:$G$23,MATCH($A6,Experiments!$A$4:$A$23,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C6" s="10" t="str">
-        <f>IFERROR(INDEX(Experiments!$H$4:$H$23,MATCH($A6,Experiments!$A$4:$A$23,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D6" s="10" t="str">
-        <f>IFERROR(INDEX(Experiments!$J$4:$J$23,MATCH($A6,Experiments!$A$4:$A$23,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E6" s="14" t="str">
-        <f>IFERROR(INDEX(Experiments!$Y$4:$Y$23,MATCH($A6,Experiments!$A$4:$A$23,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F6" s="14" t="str">
-        <f>IFERROR(INDEX(Experiments!$AB$4:$AB$23,MATCH($A6,Experiments!$A$4:$A$23,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G6" s="17" t="s">
+      <c r="B6" s="4" t="str">
+        <f>IFERROR(INDEX(Experiments!$G$4:$G$22,MATCH($A6,Experiments!$A$4:$A$22,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C6" s="4" t="str">
+        <f>IFERROR(INDEX(Experiments!$H$4:$H$22,MATCH($A6,Experiments!$A$4:$A$22,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D6" s="4" t="str">
+        <f>IFERROR(INDEX(Experiments!$J$4:$J$22,MATCH($A6,Experiments!$A$4:$A$22,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E6" s="8" t="str">
+        <f>IFERROR(INDEX(Experiments!$Y$4:$Y$22,MATCH($A6,Experiments!$A$4:$A$22,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="8" t="str">
+        <f>IFERROR(INDEX(Experiments!$AB$4:$AB$22,MATCH($A6,Experiments!$A$4:$A$22,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="10" t="str">
-        <f>IFERROR(INDEX(Experiments!$G$4:$G$23,MATCH($A7,Experiments!$A$4:$A$23,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C7" s="10" t="str">
-        <f>IFERROR(INDEX(Experiments!$H$4:$H$23,MATCH($A7,Experiments!$A$4:$A$23,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D7" s="10" t="str">
-        <f>IFERROR(INDEX(Experiments!$J$4:$J$23,MATCH($A7,Experiments!$A$4:$A$23,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E7" s="14" t="str">
-        <f>IFERROR(INDEX(Experiments!$Y$4:$Y$23,MATCH($A7,Experiments!$A$4:$A$23,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F7" s="14" t="str">
-        <f>IFERROR(INDEX(Experiments!$AB$4:$AB$23,MATCH($A7,Experiments!$A$4:$A$23,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="17" t="s">
+      <c r="B7" s="4" t="str">
+        <f>IFERROR(INDEX(Experiments!$G$4:$G$22,MATCH($A7,Experiments!$A$4:$A$22,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4" t="str">
+        <f>IFERROR(INDEX(Experiments!$H$4:$H$22,MATCH($A7,Experiments!$A$4:$A$22,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4" t="str">
+        <f>IFERROR(INDEX(Experiments!$J$4:$J$22,MATCH($A7,Experiments!$A$4:$A$22,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="8" t="str">
+        <f>IFERROR(INDEX(Experiments!$Y$4:$Y$22,MATCH($A7,Experiments!$A$4:$A$22,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="8" t="str">
+        <f>IFERROR(INDEX(Experiments!$AB$4:$AB$22,MATCH($A7,Experiments!$A$4:$A$22,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="12" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2528,372 +2638,372 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="10" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="9" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="9" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="9" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="9" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="9" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="9" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="9" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="9" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="9" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="9" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="9" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="9" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="9" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="9" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="9" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="9" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="9" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="9" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="9" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="9" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="9" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="9" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="9" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="9" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="9" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="9" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="9" t="s">
         <v>91</v>
       </c>
     </row>
@@ -2918,84 +3028,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E4" s="14"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="14"/>
+      <c r="E5" s="8"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="E6" s="14"/>
+      <c r="E6" s="8"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/ExperimentLogs.xlsx
+++ b/ExperimentLogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliverstaub/gitroot/BachelorThesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF90E13-05B6-0145-A9F6-5E1DE5D19FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A41C53-072D-644B-93A5-F637835349C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="10080" windowHeight="17940" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="15120" windowHeight="17960" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Experiments" sheetId="1" r:id="rId1"/>
@@ -217,6 +217,7 @@
         <r>
           <rPr>
             <sz val="10"/>
+            <color rgb="FF000000"/>
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
@@ -433,7 +434,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="116">
   <si>
     <t>Website-Fingerprinting Experiment Tracker  —  Tor Circuit Padding Study</t>
   </si>
@@ -769,6 +770,18 @@
   </si>
   <si>
     <t>exp-baseline-20</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>exp-padding-20</t>
+  </si>
+  <si>
+    <t>exp-reduced-20</t>
+  </si>
+  <si>
+    <t>REDUCED</t>
   </si>
 </sst>
 </file>
@@ -780,7 +793,7 @@
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\-0.0%;\-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -848,6 +861,12 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -950,7 +969,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1014,6 +1033,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="21" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1278,31 +1300,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF22"/>
+  <dimension ref="A1:AF23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="7" customWidth="1"/>
-    <col min="13" max="13" width="22" customWidth="1"/>
-    <col min="14" max="14" width="11" customWidth="1"/>
-    <col min="15" max="15" width="12" customWidth="1"/>
-    <col min="16" max="16" width="10" customWidth="1"/>
-    <col min="17" max="17" width="11" customWidth="1"/>
-    <col min="18" max="18" width="10" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="12" customWidth="1"/>
-    <col min="21" max="21" width="13" customWidth="1"/>
-    <col min="22" max="24" width="9" customWidth="1"/>
-    <col min="25" max="30" width="10" customWidth="1"/>
-    <col min="31" max="31" width="11" customWidth="1"/>
-    <col min="32" max="32" width="60.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="9" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="37.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1605,7 +1634,7 @@
       <c r="I5" s="23">
         <v>30</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="7" t="s">
         <v>110</v>
       </c>
       <c r="K5" s="24"/>
@@ -1693,7 +1722,7 @@
       <c r="I6" s="23">
         <v>30</v>
       </c>
-      <c r="J6" s="23" t="s">
+      <c r="J6" s="7" t="s">
         <v>110</v>
       </c>
       <c r="K6" s="24"/>
@@ -1753,84 +1782,181 @@
       </c>
       <c r="AF6" s="24"/>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
-      <c r="AC7" s="6"/>
-      <c r="AD7" s="6"/>
-      <c r="AE7" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A8" s="4"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="8"/>
-      <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
-      <c r="AC8" s="6"/>
-      <c r="AD8" s="6"/>
-      <c r="AE8" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AF8" s="9"/>
+    <row r="7" spans="1:32" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="23">
+        <v>0.01</v>
+      </c>
+      <c r="C7" s="23">
+        <v>79</v>
+      </c>
+      <c r="D7" s="23">
+        <v>3</v>
+      </c>
+      <c r="E7" s="23">
+        <v>303</v>
+      </c>
+      <c r="F7" s="23">
+        <v>10</v>
+      </c>
+      <c r="G7" s="23">
+        <v>20</v>
+      </c>
+      <c r="H7" s="23">
+        <v>150</v>
+      </c>
+      <c r="I7" s="23">
+        <v>30</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" s="24"/>
+      <c r="L7" s="23">
+        <v>1</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="N7" s="24"/>
+      <c r="O7" s="25">
+        <v>0.34444444444444444</v>
+      </c>
+      <c r="P7" s="23">
+        <v>3000</v>
+      </c>
+      <c r="Q7" s="23">
+        <v>150</v>
+      </c>
+      <c r="R7" s="23">
+        <v>46</v>
+      </c>
+      <c r="S7" s="26">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="T7" s="24"/>
+      <c r="U7" s="23">
+        <v>638</v>
+      </c>
+      <c r="V7" s="23">
+        <v>2430</v>
+      </c>
+      <c r="W7" s="23">
+        <v>270</v>
+      </c>
+      <c r="X7" s="23">
+        <v>300</v>
+      </c>
+      <c r="Y7" s="26">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="Z7" s="26">
+        <v>0.84199999999999997</v>
+      </c>
+      <c r="AA7" s="26">
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="AB7" s="26">
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="AC7" s="23">
+        <v>30</v>
+      </c>
+      <c r="AD7" s="24"/>
+      <c r="AE7" s="26">
+        <v>0.05</v>
+      </c>
+      <c r="AF7" s="24"/>
+    </row>
+    <row r="8" spans="1:32" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="23">
+        <v>0.01</v>
+      </c>
+      <c r="C8" s="23">
+        <v>79</v>
+      </c>
+      <c r="D8" s="23">
+        <v>3</v>
+      </c>
+      <c r="E8" s="23">
+        <v>303</v>
+      </c>
+      <c r="F8" s="23">
+        <v>10</v>
+      </c>
+      <c r="G8" s="23">
+        <v>20</v>
+      </c>
+      <c r="H8" s="23">
+        <v>150</v>
+      </c>
+      <c r="I8" s="23">
+        <v>30</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="K8" s="24"/>
+      <c r="L8" s="23">
+        <v>1</v>
+      </c>
+      <c r="M8" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="N8" s="24"/>
+      <c r="O8" s="25">
+        <v>0.34583333333333333</v>
+      </c>
+      <c r="P8" s="23">
+        <v>3000</v>
+      </c>
+      <c r="Q8" s="23">
+        <v>150</v>
+      </c>
+      <c r="R8" s="23">
+        <v>58</v>
+      </c>
+      <c r="S8" s="26">
+        <v>1.9E-2</v>
+      </c>
+      <c r="T8" s="24"/>
+      <c r="U8" s="23">
+        <v>611</v>
+      </c>
+      <c r="V8" s="23">
+        <v>2430</v>
+      </c>
+      <c r="W8" s="23">
+        <v>270</v>
+      </c>
+      <c r="X8" s="23">
+        <v>300</v>
+      </c>
+      <c r="Y8" s="26">
+        <v>0.86699999999999999</v>
+      </c>
+      <c r="Z8" s="26">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="AA8" s="26">
+        <v>0.86699999999999999</v>
+      </c>
+      <c r="AB8" s="26">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="AC8" s="23">
+        <v>30</v>
+      </c>
+      <c r="AD8" s="24"/>
+      <c r="AE8" s="26">
+        <v>0.05</v>
+      </c>
+      <c r="AF8" s="24"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
@@ -1842,7 +1968,7 @@
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
-      <c r="J9" s="7"/>
+      <c r="J9" s="6"/>
       <c r="K9" s="4"/>
       <c r="L9" s="6"/>
       <c r="M9" s="4"/>
@@ -1882,7 +2008,7 @@
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
-      <c r="J10" s="7"/>
+      <c r="J10" s="6"/>
       <c r="K10" s="4"/>
       <c r="L10" s="6"/>
       <c r="M10" s="4"/>
@@ -1922,7 +2048,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
-      <c r="J11" s="7"/>
+      <c r="J11" s="6"/>
       <c r="K11" s="4"/>
       <c r="L11" s="6"/>
       <c r="M11" s="4"/>
@@ -1962,7 +2088,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
-      <c r="J12" s="7"/>
+      <c r="J12" s="6"/>
       <c r="K12" s="4"/>
       <c r="L12" s="6"/>
       <c r="M12" s="4"/>
@@ -2002,7 +2128,7 @@
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
-      <c r="J13" s="7"/>
+      <c r="J13" s="6"/>
       <c r="K13" s="4"/>
       <c r="L13" s="6"/>
       <c r="M13" s="4"/>
@@ -2042,7 +2168,7 @@
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
-      <c r="J14" s="7"/>
+      <c r="J14" s="6"/>
       <c r="K14" s="4"/>
       <c r="L14" s="6"/>
       <c r="M14" s="4"/>
@@ -2082,7 +2208,7 @@
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
-      <c r="J15" s="7"/>
+      <c r="J15" s="6"/>
       <c r="K15" s="4"/>
       <c r="L15" s="6"/>
       <c r="M15" s="4"/>
@@ -2122,7 +2248,7 @@
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="7"/>
+      <c r="J16" s="6"/>
       <c r="K16" s="4"/>
       <c r="L16" s="6"/>
       <c r="M16" s="4"/>
@@ -2162,7 +2288,7 @@
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
-      <c r="J17" s="7"/>
+      <c r="J17" s="6"/>
       <c r="K17" s="4"/>
       <c r="L17" s="6"/>
       <c r="M17" s="4"/>
@@ -2202,7 +2328,7 @@
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
-      <c r="J18" s="7"/>
+      <c r="J18" s="6"/>
       <c r="K18" s="4"/>
       <c r="L18" s="6"/>
       <c r="M18" s="4"/>
@@ -2242,7 +2368,7 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
-      <c r="J19" s="7"/>
+      <c r="J19" s="6"/>
       <c r="K19" s="4"/>
       <c r="L19" s="6"/>
       <c r="M19" s="4"/>
@@ -2282,7 +2408,7 @@
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
-      <c r="J20" s="7"/>
+      <c r="J20" s="6"/>
       <c r="K20" s="4"/>
       <c r="L20" s="6"/>
       <c r="M20" s="4"/>
@@ -2317,12 +2443,14 @@
       <c r="B21" s="5"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
+      <c r="E21" s="27" t="s">
+        <v>112</v>
+      </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
-      <c r="J21" s="7"/>
+      <c r="J21" s="6"/>
       <c r="K21" s="4"/>
       <c r="L21" s="6"/>
       <c r="M21" s="4"/>
@@ -2362,7 +2490,7 @@
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
-      <c r="J22" s="7"/>
+      <c r="J22" s="6"/>
       <c r="K22" s="4"/>
       <c r="L22" s="6"/>
       <c r="M22" s="4"/>
@@ -2392,6 +2520,9 @@
       </c>
       <c r="AF22" s="9"/>
     </row>
+    <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J23" s="6"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:AF1"/>
@@ -2400,7 +2531,7 @@
     <mergeCell ref="Y2:AF2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="J4 J7:J22" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J4:J6" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"OFF,ON,Reduced"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/ExperimentLogs.xlsx
+++ b/ExperimentLogs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliverstaub/gitroot/BachelorThesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A41C53-072D-644B-93A5-F637835349C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF77960-D938-8B44-8747-556A63CCC57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="15120" windowHeight="17960" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17940" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Experiments" sheetId="1" r:id="rId1"/>
@@ -434,7 +434,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="117">
   <si>
     <t>Website-Fingerprinting Experiment Tracker  —  Tor Circuit Padding Study</t>
   </si>
@@ -782,6 +782,9 @@
   </si>
   <si>
     <t>REDUCED</t>
+  </si>
+  <si>
+    <t>exp-baseline-80</t>
   </si>
 </sst>
 </file>
@@ -793,13 +796,20 @@
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\-0.0%;\-"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -845,6 +855,14 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
@@ -870,7 +888,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -913,8 +931,26 @@
         <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -965,79 +1001,159 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="21" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="21" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="1" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="5" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="3" applyBorder="1"/>
+    <xf numFmtId="21" fontId="1" fillId="10" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="10" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="2" applyBorder="1"/>
+    <xf numFmtId="21" fontId="1" fillId="9" borderId="5" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="9" borderId="5" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="20% - Accent1" xfId="1" builtinId="30"/>
+    <cellStyle name="20% - Accent4" xfId="2" builtinId="42"/>
+    <cellStyle name="20% - Accent6" xfId="3" builtinId="50"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1370,7 +1486,7 @@
       <c r="AE1" s="16"/>
       <c r="AF1" s="16"/>
     </row>
-    <row r="2" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
@@ -1410,7 +1526,7 @@
       <c r="AE2" s="19"/>
       <c r="AF2" s="19"/>
     </row>
-    <row r="3" spans="1:32" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1634,7 +1750,7 @@
       <c r="I5" s="23">
         <v>30</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="28" t="s">
         <v>110</v>
       </c>
       <c r="K5" s="24"/>
@@ -1694,349 +1810,377 @@
       </c>
       <c r="AF5" s="24"/>
     </row>
-    <row r="6" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:32" s="30" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="30">
         <v>0.01</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="30">
         <v>79</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="30">
         <v>3</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="30">
         <v>303</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="30">
         <v>10</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="30">
         <v>20</v>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="30">
         <v>150</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="30">
         <v>30</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="K6" s="24"/>
-      <c r="L6" s="23">
+      <c r="L6" s="30">
         <v>1</v>
       </c>
-      <c r="M6" s="23" t="s">
+      <c r="M6" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="N6" s="24"/>
-      <c r="O6" s="25">
+      <c r="O6" s="32">
         <v>0.33124999999999999</v>
       </c>
-      <c r="P6" s="23">
+      <c r="P6" s="30">
         <v>3000</v>
       </c>
-      <c r="Q6" s="23">
+      <c r="Q6" s="30">
         <v>150</v>
       </c>
-      <c r="R6" s="23">
+      <c r="R6" s="30">
         <v>51</v>
       </c>
-      <c r="S6" s="26">
+      <c r="S6" s="33">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="T6" s="24"/>
-      <c r="U6" s="23">
+      <c r="U6" s="30">
         <v>635</v>
       </c>
-      <c r="V6" s="23">
+      <c r="V6" s="30">
         <v>2430</v>
       </c>
-      <c r="W6" s="23">
+      <c r="W6" s="30">
         <v>270</v>
       </c>
-      <c r="X6" s="23">
+      <c r="X6" s="30">
         <v>300</v>
       </c>
-      <c r="Y6" s="26">
+      <c r="Y6" s="33">
         <v>0.92700000000000005</v>
       </c>
-      <c r="Z6" s="26">
+      <c r="Z6" s="33">
         <v>0.93300000000000005</v>
       </c>
-      <c r="AA6" s="26">
+      <c r="AA6" s="33">
         <v>0.92700000000000005</v>
       </c>
-      <c r="AB6" s="26">
+      <c r="AB6" s="33">
         <v>0.92700000000000005</v>
       </c>
-      <c r="AC6" s="23">
+      <c r="AC6" s="30">
         <v>30</v>
       </c>
-      <c r="AD6" s="24"/>
-      <c r="AE6" s="26">
+      <c r="AE6" s="33">
         <v>0.05</v>
       </c>
-      <c r="AF6" s="24"/>
-    </row>
-    <row r="7" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="22" t="s">
+    </row>
+    <row r="7" spans="1:32" s="35" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="35">
         <v>0.01</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="35">
         <v>79</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="35">
         <v>3</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="35">
         <v>303</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="35">
         <v>10</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="35">
         <v>20</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="35">
         <v>150</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="35">
         <v>30</v>
       </c>
-      <c r="J7" s="23" t="s">
+      <c r="J7" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="24"/>
-      <c r="L7" s="23">
+      <c r="L7" s="35">
         <v>1</v>
       </c>
-      <c r="M7" s="23" t="s">
+      <c r="M7" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="N7" s="24"/>
-      <c r="O7" s="25">
+      <c r="O7" s="36">
         <v>0.34444444444444444</v>
       </c>
-      <c r="P7" s="23">
+      <c r="P7" s="35">
         <v>3000</v>
       </c>
-      <c r="Q7" s="23">
+      <c r="Q7" s="35">
         <v>150</v>
       </c>
-      <c r="R7" s="23">
+      <c r="R7" s="35">
         <v>46</v>
       </c>
-      <c r="S7" s="26">
+      <c r="S7" s="37">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="T7" s="24"/>
-      <c r="U7" s="23">
+      <c r="U7" s="35">
         <v>638</v>
       </c>
-      <c r="V7" s="23">
+      <c r="V7" s="35">
         <v>2430</v>
       </c>
-      <c r="W7" s="23">
+      <c r="W7" s="35">
         <v>270</v>
       </c>
-      <c r="X7" s="23">
+      <c r="X7" s="35">
         <v>300</v>
       </c>
-      <c r="Y7" s="26">
+      <c r="Y7" s="37">
         <v>0.83299999999999996</v>
       </c>
-      <c r="Z7" s="26">
+      <c r="Z7" s="37">
         <v>0.84199999999999997</v>
       </c>
-      <c r="AA7" s="26">
+      <c r="AA7" s="37">
         <v>0.83299999999999996</v>
       </c>
-      <c r="AB7" s="26">
+      <c r="AB7" s="37">
         <v>0.82799999999999996</v>
       </c>
-      <c r="AC7" s="23">
+      <c r="AC7" s="35">
         <v>30</v>
       </c>
-      <c r="AD7" s="24"/>
-      <c r="AE7" s="26">
+      <c r="AE7" s="37">
         <v>0.05</v>
       </c>
-      <c r="AF7" s="24"/>
-    </row>
-    <row r="8" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="22" t="s">
+    </row>
+    <row r="8" spans="1:32" s="38" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="38">
         <v>0.01</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="38">
         <v>79</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="38">
         <v>3</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="38">
         <v>303</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="38">
         <v>10</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="38">
         <v>20</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="38">
         <v>150</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="38">
         <v>30</v>
       </c>
-      <c r="J8" s="23" t="s">
+      <c r="J8" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="K8" s="24"/>
-      <c r="L8" s="23">
+      <c r="L8" s="38">
         <v>1</v>
       </c>
-      <c r="M8" s="23" t="s">
+      <c r="M8" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="N8" s="24"/>
-      <c r="O8" s="25">
+      <c r="O8" s="39">
         <v>0.34583333333333333</v>
       </c>
-      <c r="P8" s="23">
+      <c r="P8" s="38">
         <v>3000</v>
       </c>
-      <c r="Q8" s="23">
+      <c r="Q8" s="38">
         <v>150</v>
       </c>
-      <c r="R8" s="23">
+      <c r="R8" s="38">
         <v>58</v>
       </c>
-      <c r="S8" s="26">
+      <c r="S8" s="40">
         <v>1.9E-2</v>
       </c>
-      <c r="T8" s="24"/>
-      <c r="U8" s="23">
+      <c r="U8" s="38">
         <v>611</v>
       </c>
-      <c r="V8" s="23">
+      <c r="V8" s="38">
         <v>2430</v>
       </c>
-      <c r="W8" s="23">
+      <c r="W8" s="38">
         <v>270</v>
       </c>
-      <c r="X8" s="23">
+      <c r="X8" s="38">
         <v>300</v>
       </c>
-      <c r="Y8" s="26">
+      <c r="Y8" s="40">
         <v>0.86699999999999999</v>
       </c>
-      <c r="Z8" s="26">
+      <c r="Z8" s="40">
         <v>0.88100000000000001</v>
       </c>
-      <c r="AA8" s="26">
+      <c r="AA8" s="40">
         <v>0.86699999999999999</v>
       </c>
-      <c r="AB8" s="26">
+      <c r="AB8" s="40">
         <v>0.86299999999999999</v>
       </c>
-      <c r="AC8" s="23">
+      <c r="AC8" s="38">
         <v>30</v>
       </c>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="26">
+      <c r="AE8" s="40">
         <v>0.05</v>
       </c>
-      <c r="AF8" s="24"/>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="8" t="str">
+    </row>
+    <row r="9" spans="1:32" s="30" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="30">
+        <v>0.01</v>
+      </c>
+      <c r="C9" s="30">
+        <v>79</v>
+      </c>
+      <c r="D9" s="30">
+        <v>3</v>
+      </c>
+      <c r="E9" s="30">
+        <v>313</v>
+      </c>
+      <c r="F9" s="30">
+        <v>20</v>
+      </c>
+      <c r="G9" s="30">
+        <v>80</v>
+      </c>
+      <c r="H9" s="30">
+        <v>150</v>
+      </c>
+      <c r="I9" s="30">
+        <v>30</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="L9" s="30">
+        <v>1</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="O9" s="32">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="P9" s="30">
+        <v>12000</v>
+      </c>
+      <c r="Q9" s="30">
+        <v>150</v>
+      </c>
+      <c r="R9" s="30">
+        <v>523</v>
+      </c>
+      <c r="S9" s="33">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="U9" s="30">
+        <v>583</v>
+      </c>
+      <c r="V9" s="30">
+        <v>9720</v>
+      </c>
+      <c r="W9" s="30">
+        <v>1080</v>
+      </c>
+      <c r="X9" s="30">
+        <v>1200</v>
+      </c>
+      <c r="Y9" s="33">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="Z9" s="33">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="AA9" s="33">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="AB9" s="33">
+        <v>0.81399999999999995</v>
+      </c>
+      <c r="AC9" s="30">
+        <v>30</v>
+      </c>
+      <c r="AE9" s="33">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A10" s="41"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="8"/>
-      <c r="AA9" s="8"/>
-      <c r="AB9" s="8"/>
-      <c r="AC9" s="6"/>
-      <c r="AD9" s="6"/>
-      <c r="AE9" s="8" t="str">
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="43"/>
+      <c r="X10" s="43"/>
+      <c r="Y10" s="44"/>
+      <c r="Z10" s="44"/>
+      <c r="AA10" s="44"/>
+      <c r="AB10" s="44"/>
+      <c r="AC10" s="43"/>
+      <c r="AD10" s="43"/>
+      <c r="AE10" s="44" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AF9" s="9"/>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="8"/>
-      <c r="AA10" s="8"/>
-      <c r="AB10" s="8"/>
-      <c r="AC10" s="6"/>
-      <c r="AD10" s="6"/>
-      <c r="AE10" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AF10" s="9"/>
+      <c r="AF10" s="45"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
